--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Abr 25 R</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45748</v>
+        <v>45597</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>111.6</v>
+        <v>111</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>May 25 R</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45778</v>
+        <v>45627</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>110.1</v>
+        <v>109.4</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jun 25 R</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45809</v>
+        <v>45658</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>111.5</v>
+        <v>108.6</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -751,18 +751,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Jul 25 R</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45839</v>
+        <v>45689</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>111.2</v>
+        <v>110.2</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Ago 25 R</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45870</v>
+        <v>45717</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>112.1</v>
+        <v>110.2</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Sep 25 R</t>
+          <t>Abr 25 R</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45901</v>
+        <v>45748</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>112.4</v>
+        <v>111.6</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Oct 25 R</t>
+          <t>May 25 R</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45931</v>
+        <v>45778</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>113.5</v>
+        <v>110.1</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Nov 25 R</t>
+          <t>Jun 25 R</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45962</v>
+        <v>45809</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>112.9</v>
+        <v>111.5</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Dic 25 R</t>
+          <t>Jul 25 R</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45992</v>
+        <v>45839</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>114.4</v>
+        <v>111.2</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Ene 26 R</t>
+          <t>Ago 25 R</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>46023</v>
+        <v>45870</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>112.1</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Feb 26 R</t>
+          <t>Sep 25 R</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>46054</v>
+        <v>45901</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>111.4</v>
+        <v>112.4</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Oct 25 R</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>46082</v>
+        <v>45931</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>113.6</v>
+        <v>113.5</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Revisado</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1273,18 +1273,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Nov 25 R</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>46113</v>
+        <v>45962</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>113.7</v>
+        <v>112.9</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Definitivo</t>
+          <t>Revisado</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1331,56 +1331,346 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>Dic 25 R</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ene 26 R</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+2.7%</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26 R</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Mar 26 P</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+3.1%</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B24" s="5" t="n">
         <v>46143</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C24" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>+0.1%</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>+2.6%</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>05 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Oct 24</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45597</v>
+        <v>45566</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>111</v>
+        <v>110.5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>109.4</v>
+        <v>111</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>108.6</v>
+        <v>109.4</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -751,18 +751,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>110.2</v>
+        <v>108.6</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>110.2</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Abr 25 R</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>111.6</v>
+        <v>110.2</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>May 25 R</t>
+          <t>Abr 25 R</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>110.1</v>
+        <v>111.6</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Jun 25 R</t>
+          <t>May 25 R</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>111.5</v>
+        <v>110.1</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Jul 25 R</t>
+          <t>Jun 25 R</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>111.2</v>
+        <v>111.5</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Ago 25 R</t>
+          <t>Jul 25 R</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>112.1</v>
+        <v>111.2</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Sep 25 R</t>
+          <t>Ago 25 R</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>112.4</v>
+        <v>112.1</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Oct 25 R</t>
+          <t>Sep 25 R</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>113.5</v>
+        <v>112.4</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1273,18 +1273,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Nov 25 R</t>
+          <t>Oct 25 R</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>112.9</v>
+        <v>113.5</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1331,18 +1331,18 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Dic 25 R</t>
+          <t>Nov 25 R</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>114.4</v>
+        <v>112.9</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1389,18 +1389,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ene 26 R</t>
+          <t>Dic 25 R</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>112.1</v>
+        <v>114.4</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1447,18 +1447,18 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Feb 26 R</t>
+          <t>Ene 26 R</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>111.4</v>
+        <v>112.1</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1505,18 +1505,18 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Feb 26 R</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>113.6</v>
+        <v>111.4</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Revisado</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1563,18 +1563,18 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Mar 26 P</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>113.7</v>
+        <v>113.6</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Definitivo</t>
+          <t>Preliminar</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -1621,56 +1621,114 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B25" s="8" t="n">
         <v>46143</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C25" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>+0.1%</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>+2.6%</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>05 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf · Fecha de publicación: 05 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -925,7 +925,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Abr 25 R</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>May 25 R</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Jun 25 R</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Jul 25 R</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ago 25 R</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Sep 25 R</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Oct 25 R</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Nov 25 R</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Dic 25 R</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Ene 26 R</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Feb 26 R</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">

--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:AQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -485,23 +485,57 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="55" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Indicador mensual del consumo privado</t>
+          <t>Indicador Mensual del Consumo Privado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 / Porcentaje</t>
         </is>
       </c>
     </row>
@@ -530,30 +564,200 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Var. mensual (%)</t>
+          <t>Var. mensual total (%)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Var. anual (%)</t>
+          <t>Var. anual total (%)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>Var. anual original total (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes total (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Var. mensual nacional (%)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual nacional (%)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Var. mensual bienes nacionales (%)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual bienes nacionales (%)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Var. mensual servicios nacionales (%)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual servicios nacionales (%)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Var. mensual importado (%)</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual importado (%)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Var. mensual bienes importados (%)</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual bienes importados (%)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original nacional (%)</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes nacional (%)</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes nacionales (%)</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes nacionales (%)</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original servicios nacionales (%)</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes servicios nacionales (%)</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original importado (%)</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes importado (%)</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes importados (%)</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes importados (%)</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes semi duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes semi duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes no duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes no duraderos nacionales (%)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes semi duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes semi duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual original bienes no duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Acumulado ene-mes bienes no duraderos importados (%)</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
           <t>Carácter del dato</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr">
         <is>
           <t>URL del boletín</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <t>Fecha de publicación</t>
         </is>
@@ -577,22 +781,120 @@
       <c r="E6" s="7" t="n">
         <v>0.005</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T6" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="W6" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="X6" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="Z6" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA6" s="7" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AB6" s="7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AC6" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD6" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AE6" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AF6" s="7" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="AG6" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AH6" s="7" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AI6" s="7" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AJ6" s="7" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AK6" s="7" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AL6" s="7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AM6" s="7" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AN6" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="AO6" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="AP6" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="AQ6" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -616,22 +918,124 @@
       <c r="E7" s="10" t="n">
         <v>0.007</v>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Q7" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R7" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S7" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T7" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="V7" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="W7" s="10" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="X7" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="Z7" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AA7" s="10" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AB7" s="10" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AC7" s="10" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AD7" s="10" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="AE7" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AF7" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AG7" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AH7" s="10" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AI7" s="10" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AJ7" s="10" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AK7" s="10" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AL7" s="10" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="AM7" s="10" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AN7" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="AO7" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="AP7" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="AQ7" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -655,22 +1059,124 @@
       <c r="E8" s="7" t="n">
         <v>-0.008</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="W8" s="7" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Z8" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AA8" s="7" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AB8" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AC8" s="7" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AD8" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AE8" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AF8" s="7" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="AG8" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AH8" s="7" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="AI8" s="7" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AJ8" s="7" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AK8" s="7" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="AL8" s="7" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AM8" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN8" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="AO8" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="AP8" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="AQ8" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -694,22 +1200,76 @@
       <c r="E9" s="10" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n"/>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="10" t="n"/>
+      <c r="AH9" s="10" t="n"/>
+      <c r="AI9" s="10" t="n"/>
+      <c r="AJ9" s="10" t="n"/>
+      <c r="AK9" s="10" t="n"/>
+      <c r="AL9" s="10" t="n"/>
+      <c r="AM9" s="10" t="n"/>
+      <c r="AN9" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="AO9" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="AP9" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="AQ9" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -733,22 +1293,124 @@
       <c r="E10" s="7" t="n">
         <v>-0.007</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="W10" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>-0.092</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="Z10" s="7" t="n">
+        <v>-0.092</v>
+      </c>
+      <c r="AA10" s="7" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="AB10" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC10" s="7" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AD10" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AE10" s="7" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="AF10" s="7" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="AG10" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AH10" s="7" t="n">
+        <v>-0.119</v>
+      </c>
+      <c r="AI10" s="7" t="n">
+        <v>-0.127</v>
+      </c>
+      <c r="AJ10" s="7" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="AK10" s="7" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="AL10" s="7" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AM10" s="7" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="AN10" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="AO10" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="AP10" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="AQ10" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -772,22 +1434,124 @@
       <c r="E11" s="10" t="n">
         <v>-0.013</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="V11" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W11" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="Z11" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AA11" s="10" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="AB11" s="10" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AC11" s="10" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AE11" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AF11" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AG11" s="10" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AH11" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AI11" s="10" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="AJ11" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AM11" s="10" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="AN11" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="AO11" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="AP11" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="AQ11" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -811,22 +1575,124 @@
       <c r="E12" s="7" t="n">
         <v>0.007</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>-0.083</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>-0.083</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="W12" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="AA12" s="7" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AC12" s="7" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AD12" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AE12" s="7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AF12" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AG12" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AH12" s="7" t="n">
+        <v>-0.188</v>
+      </c>
+      <c r="AI12" s="7" t="n">
+        <v>-0.116</v>
+      </c>
+      <c r="AJ12" s="7" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="AK12" s="7" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="AL12" s="7" t="n">
+        <v>-0.144</v>
+      </c>
+      <c r="AM12" s="7" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="AN12" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="AO12" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="AQ12" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -850,22 +1716,124 @@
       <c r="E13" s="10" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S13" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="W13" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X13" s="10" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="Z13" s="10" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="AA13" s="10" t="n">
+        <v>-0.076</v>
+      </c>
+      <c r="AB13" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AC13" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="AE13" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AF13" s="10" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AG13" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AH13" s="10" t="n">
+        <v>-0.116</v>
+      </c>
+      <c r="AI13" s="10" t="n">
+        <v>-0.116</v>
+      </c>
+      <c r="AJ13" s="10" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="AK13" s="10" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="AL13" s="10" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="AN13" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="AO13" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="AP13" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="AQ13" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -889,22 +1857,124 @@
       <c r="E14" s="7" t="n">
         <v>0.011</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="T14" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="U14" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="W14" s="7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="AA14" s="7" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="AB14" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AC14" s="7" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AD14" s="7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AE14" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AF14" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AG14" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AH14" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AI14" s="7" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="AJ14" s="7" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AK14" s="7" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AL14" s="7" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AM14" s="7" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AN14" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="AO14" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="AQ14" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -928,22 +1998,124 @@
       <c r="E15" s="10" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="S15" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="V15" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W15" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="X15" s="10" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="Z15" s="10" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AA15" s="10" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="AB15" s="10" t="n">
+        <v>-0.079</v>
+      </c>
+      <c r="AC15" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AD15" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AE15" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AF15" s="10" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="AG15" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AH15" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AI15" s="10" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="AJ15" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK15" s="10" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AL15" s="10" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AM15" s="10" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="AN15" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="AO15" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="AP15" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="AQ15" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -967,22 +2139,124 @@
       <c r="E16" s="7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W16" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AA16" s="7" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="AC16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AD16" s="7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AE16" s="7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AF16" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AG16" s="7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AH16" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AI16" s="7" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="AJ16" s="7" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AK16" s="7" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="AL16" s="7" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AM16" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AN16" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="AO16" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="AP16" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="AQ16" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1006,22 +2280,124 @@
       <c r="E17" s="10" t="n">
         <v>0.021</v>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T17" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="V17" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="W17" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="X17" s="10" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="Y17" s="10" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="Z17" s="10" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AA17" s="10" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="AB17" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AC17" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AD17" s="10" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="AE17" s="10" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="AF17" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AG17" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AH17" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI17" s="10" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="AJ17" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AK17" s="10" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="AL17" s="10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AM17" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AN17" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="AO17" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="AP17" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="AQ17" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1045,22 +2421,124 @@
       <c r="E18" s="7" t="n">
         <v>0.041</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="W18" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AA18" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AC18" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AD18" s="7" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="AE18" s="7" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="AF18" s="7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AG18" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AH18" s="7" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="AI18" s="7" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AJ18" s="7" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="AK18" s="7" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="AL18" s="7" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AM18" s="7" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AN18" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="AO18" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="AP18" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="AQ18" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1084,22 +2562,124 @@
       <c r="E19" s="10" t="n">
         <v>0.028</v>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="V19" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="W19" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X19" s="10" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Y19" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Z19" s="10" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="AA19" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" s="10" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AC19" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AD19" s="10" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="AE19" s="10" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AF19" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AG19" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AH19" s="10" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AI19" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AJ19" s="10" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="AK19" s="10" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="AL19" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AM19" s="10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AN19" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="AO19" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="AP19" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="AQ19" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1123,22 +2703,124 @@
       <c r="E20" s="7" t="n">
         <v>0.056</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="T20" s="7" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="W20" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="X20" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="Z20" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA20" s="7" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AB20" s="7" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AC20" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AD20" s="7" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AE20" s="7" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AF20" s="7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG20" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AH20" s="7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AI20" s="7" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AJ20" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AK20" s="7" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="AL20" s="7" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AM20" s="7" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AN20" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="AO20" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="AP20" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="AQ20" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1162,22 +2844,76 @@
       <c r="E21" s="10" t="n">
         <v>0.027</v>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="10" t="n"/>
+      <c r="AJ21" s="10" t="n"/>
+      <c r="AK21" s="10" t="n"/>
+      <c r="AL21" s="10" t="n"/>
+      <c r="AM21" s="10" t="n"/>
+      <c r="AN21" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="AO21" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="AP21" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="AQ21" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1201,22 +2937,124 @@
       <c r="E22" s="7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="S22" s="7" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="T22" s="7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U22" s="7" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="V22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="X22" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="Z22" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AA22" s="7" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AB22" s="7" t="n">
+        <v>-0.204</v>
+      </c>
+      <c r="AC22" s="7" t="n">
+        <v>-0.122</v>
+      </c>
+      <c r="AD22" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AE22" s="7" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="AF22" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AG22" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AH22" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI22" s="7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AJ22" s="7" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="AK22" s="7" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="AL22" s="7" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AM22" s="7" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="AN22" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="AO22" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="AP22" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="AQ22" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1240,22 +3078,124 @@
       <c r="E23" s="10" t="n">
         <v>0.031</v>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="10" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="T23" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="X23" s="10" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="Y23" s="10" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="Z23" s="10" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AA23" s="10" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AB23" s="10" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="AC23" s="10" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="AD23" s="10" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="AE23" s="10" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="AF23" s="10" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AG23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="10" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AI23" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ23" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AK23" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AL23" s="10" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AM23" s="10" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AN23" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="AO23" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="AP23" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="AQ23" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1279,22 +3219,124 @@
       <c r="E24" s="7" t="n">
         <v>0.021</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="T24" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="V24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X24" s="7" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="Y24" s="7" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="Z24" s="7" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AA24" s="7" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AB24" s="7" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="AC24" s="7" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="AD24" s="7" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="AE24" s="7" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="AF24" s="7" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AG24" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AH24" s="7" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AI24" s="7" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AJ24" s="7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AK24" s="7" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="AL24" s="7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AM24" s="7" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="AN24" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="AO24" s="8" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="AP24" s="8" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="AQ24" s="8" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1318,22 +3360,124 @@
       <c r="E25" s="10" t="n">
         <v>0.026</v>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="V25" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="W25" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Y25" s="10" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="Z25" s="10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA25" s="10" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AB25" s="10" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="AC25" s="10" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="AD25" s="10" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="AE25" s="10" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AF25" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AG25" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AH25" s="10" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AI25" s="10" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="AJ25" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK25" s="10" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="AL25" s="10" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AN25" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="AO25" s="11" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="AP25" s="11" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="AQ25" s="11" t="inlineStr">
         <is>
           <t>5 de agosto de 2026</t>
         </is>
@@ -1341,9 +3485,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:AQ1"/>
+    <mergeCell ref="A3:AQ3"/>
+    <mergeCell ref="A2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="AP6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ6" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="AP7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ7" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="AP8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ8" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AP9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ9" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AP10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ10" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="AP11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ11" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="AP12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ12" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="AP13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ13" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="AP14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ14" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="AP15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ15" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AP16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ16" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="AP17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ17" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="AP18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ18" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="AP20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ20" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="AP22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ22" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AP23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ23" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AP24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ24" s="8" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,153 @@
       </c>
       <c r="AP25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
         </is>
       </c>
       <c r="AQ25" s="11" t="inlineStr">
         <is>
-          <t>5 de agosto de 2026</t>
+          <t>4 de septiembre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T26" s="7" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="U26" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V26" s="7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W26" s="7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X26" s="7" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="Y26" s="7" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="Z26" s="7" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="AA26" s="7" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AB26" s="7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AC26" s="7" t="n">
+        <v>-0.051</v>
+      </c>
+      <c r="AD26" s="7" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AE26" s="7" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="AF26" s="7" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AG26" s="7" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AH26" s="7" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AI26" s="7" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AJ26" s="7" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="AK26" s="7" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="AL26" s="7" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="AM26" s="7" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AN26" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="AO26" s="8" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="AP26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="AQ26" s="8" t="inlineStr">
+        <is>
+          <t>4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
